--- a/artfynd/S 420-2026 artfynd.xlsx
+++ b/artfynd/S 420-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127884408</v>
+        <v>137365725</v>
       </c>
       <c r="B4" t="n">
-        <v>56845</v>
+        <v>58047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100053</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,29 +962,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>905 83 Sörmjöle, Vb</t>
+          <t>Strupen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745265</v>
+        <v>739731</v>
       </c>
       <c r="R4" t="n">
-        <v>7067204</v>
+        <v>7067834</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +1002,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:32</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:32</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,20 +1022,266 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Sören  Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören  Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137365725</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137365726</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strupen, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>739731</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7067834</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sören  Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sören  Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137365726</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127884408</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>905 83 Sörmjöle, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>745265</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7067204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:32</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Via Johan Möller</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127884408</t>
         </is>
@@ -1062,6 +1292,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 420-2026 artfynd.xlsx
+++ b/artfynd/S 420-2026 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>137365725</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>137365726</v>
       </c>
       <c r="B5" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 420-2026 artfynd.xlsx
+++ b/artfynd/S 420-2026 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>137365725</v>
       </c>
       <c r="B4" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>137365726</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
